--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484177_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484177_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>,. VICENTE SABARIEGO</t>
+          <t>D. TUGORES SOTO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.6731</v>
+        <v>3.8774</v>
       </c>
       <c r="E2" t="n">
-        <v>3.1177</v>
+        <v>4.4055</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5555</v>
+        <v>-0.5282</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2281</v>
+        <v>-1.1817</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2281</v>
+        <v>1.3861</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>-2.5678</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2281</v>
+        <v>0.3136</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2281</v>
+        <v>2.2337</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>-1.9201</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>-1.4953</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>-0.8476</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>-0.6477000000000001</v>
       </c>
       <c r="P2" t="n">
-        <v>-1.9838</v>
+        <v>1.1903</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.9838</v>
+        <v>-0.9919</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>2.1822</v>
       </c>
       <c r="S2" t="n">
-        <v>3.6192</v>
+        <v>1.2612</v>
       </c>
       <c r="T2" t="n">
-        <v>3.401</v>
+        <v>1.2698</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2182</v>
+        <v>-0.0086</v>
       </c>
       <c r="V2" t="n">
-        <v>1.8097</v>
+        <v>2.6076</v>
       </c>
       <c r="W2" t="n">
-        <v>1.4724</v>
+        <v>3.8141</v>
       </c>
       <c r="X2" t="n">
-        <v>0.3373</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. TUGORES SOTO</t>
+          <t>. VICENTE SABARIEGO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,75 +643,71 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.6444</v>
+        <v>2.6369</v>
       </c>
       <c r="E3" t="n">
-        <v>4.1165</v>
+        <v>1.1993</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.4721</v>
+        <v>1.4376</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.1817</v>
+        <v>0.1046</v>
       </c>
       <c r="H3" t="n">
-        <v>1.3861</v>
+        <v>0.2212</v>
       </c>
       <c r="I3" t="n">
-        <v>-2.5678</v>
+        <v>-0.1165</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3136</v>
+        <v>0.2016</v>
       </c>
       <c r="K3" t="n">
-        <v>2.2337</v>
+        <v>0.2016</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.9201</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.4953</v>
+        <v>-0.097</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.8476</v>
+        <v>0.0195</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.6477000000000001</v>
+        <v>-0.1165</v>
       </c>
       <c r="P3" t="n">
-        <v>1.1903</v>
+        <v>1.5871</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.1822</v>
+        <v>1.5871</v>
       </c>
       <c r="S3" t="n">
-        <v>1.0282</v>
+        <v>0.9452</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9807</v>
+        <v>0.9977</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0475</v>
+        <v>-0.0525</v>
       </c>
       <c r="V3" t="n">
-        <v>2.6076</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>3.8141</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.2065</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>B. GASSAMA KARGBO</t>
-        </is>
-      </c>
+      <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
           <t>TIBU-RON CASTELLDEFELS</t>
@@ -721,58 +717,58 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.3861</v>
+        <v>2.6369</v>
       </c>
       <c r="E4" t="n">
-        <v>1.1251</v>
+        <v>1.1993</v>
       </c>
       <c r="F4" t="n">
-        <v>2.2609</v>
+        <v>1.4376</v>
       </c>
       <c r="G4" t="n">
-        <v>1.8239</v>
+        <v>0.1046</v>
       </c>
       <c r="H4" t="n">
-        <v>1.6477</v>
+        <v>0.2212</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1762</v>
+        <v>-0.1165</v>
       </c>
       <c r="J4" t="n">
-        <v>1.0684</v>
+        <v>0.2016</v>
       </c>
       <c r="K4" t="n">
-        <v>1.0282</v>
+        <v>0.2016</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0402</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>0.7554999999999999</v>
+        <v>-0.097</v>
       </c>
       <c r="N4" t="n">
-        <v>0.6195000000000001</v>
+        <v>0.0195</v>
       </c>
       <c r="O4" t="n">
-        <v>0.136</v>
+        <v>-0.1165</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.1984</v>
+        <v>1.5871</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.7935</v>
+        <v>1.5871</v>
       </c>
       <c r="S4" t="n">
-        <v>1.7605</v>
+        <v>0.9452</v>
       </c>
       <c r="T4" t="n">
-        <v>1.0487</v>
+        <v>0.9977</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7119</v>
+        <v>-0.0525</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +783,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>G. LOZANO MASSANET</t>
+          <t>B. GASSAMA KARGBO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,58 +795,58 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1145</v>
+        <v>2.5495</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.2916</v>
+        <v>0.513</v>
       </c>
       <c r="F5" t="n">
-        <v>1.406</v>
+        <v>2.0365</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8923</v>
+        <v>1.8239</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4635</v>
+        <v>1.6477</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4288</v>
+        <v>0.1762</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2072</v>
+        <v>1.0684</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3226</v>
+        <v>1.0282</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.1154</v>
+        <v>0.0402</v>
       </c>
       <c r="M5" t="n">
-        <v>0.6851</v>
+        <v>0.7554999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1409</v>
+        <v>0.6195000000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>0.5442</v>
+        <v>0.136</v>
       </c>
       <c r="P5" t="n">
-        <v>0.7935</v>
+        <v>-0.1984</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.9919</v>
       </c>
       <c r="R5" t="n">
         <v>0.7935</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5713</v>
+        <v>0.9239000000000001</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4988</v>
+        <v>0.4365</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0726</v>
+        <v>0.4874</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -863,7 +859,11 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>,. VICENTE SABARIEGO</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>TIBU-RON CASTELLDEFELS</t>
@@ -873,73 +873,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.765</v>
+        <v>1.539</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2518</v>
+        <v>1.0771</v>
       </c>
       <c r="F6" t="n">
-        <v>1.0167</v>
+        <v>0.4619</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1046</v>
+        <v>0.2281</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2212</v>
+        <v>0.2281</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1165</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2016</v>
+        <v>0.2281</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2016</v>
+        <v>0.2281</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.097</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0195</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.1165</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.5871</v>
+        <v>-1.9838</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.9838</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5871</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.9267</v>
+        <v>1.4851</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4534</v>
+        <v>1.3604</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4733</v>
+        <v>0.1247</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.8097</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.4724</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>0.3373</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>. VICENTE SABARIEGO</t>
+          <t>G. LOZANO MASSANET</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -951,58 +951,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.765</v>
+        <v>1.5328</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2518</v>
+        <v>0.0145</v>
       </c>
       <c r="F7" t="n">
-        <v>1.0167</v>
+        <v>1.5183</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1046</v>
+        <v>0.8923</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2212</v>
+        <v>0.4635</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1165</v>
+        <v>0.4288</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2016</v>
+        <v>0.2072</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2016</v>
+        <v>0.3226</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>-0.1154</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.097</v>
+        <v>0.6851</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0195</v>
+        <v>0.1409</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.1165</v>
+        <v>0.5442</v>
       </c>
       <c r="P7" t="n">
-        <v>1.5871</v>
+        <v>0.7935</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5871</v>
+        <v>0.7935</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.9267</v>
+        <v>-0.153</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4534</v>
+        <v>-0.1927</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4733</v>
+        <v>0.0396</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1029,13 +1029,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5319</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E8" t="n">
         <v>0.0403</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4916</v>
+        <v>0.5196</v>
       </c>
       <c r="G8" t="n">
         <v>-0.1613</v>
@@ -1074,13 +1074,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0187</v>
+        <v>0.0468</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0187</v>
+        <v>0.0468</v>
       </c>
       <c r="V8" t="n">
         <v>0.6745</v>
@@ -1095,7 +1095,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. ARNAL DIAZ</t>
+          <t>P. SAIZ FUENTES</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1107,73 +1107,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0094</v>
+        <v>0.4292</v>
       </c>
       <c r="E9" t="n">
-        <v>0.004</v>
+        <v>0.3019</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0054</v>
+        <v>0.1273</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6065</v>
+        <v>-0.0291</v>
       </c>
       <c r="H9" t="n">
-        <v>0.872</v>
+        <v>0.6395</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2656</v>
+        <v>-0.6686</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.0244</v>
+        <v>1.9464</v>
       </c>
       <c r="K9" t="n">
-        <v>0.6558</v>
+        <v>2.0968</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6802</v>
+        <v>-0.1504</v>
       </c>
       <c r="M9" t="n">
-        <v>0.6309</v>
+        <v>-1.9755</v>
       </c>
       <c r="N9" t="n">
-        <v>0.2163</v>
+        <v>-1.4573</v>
       </c>
       <c r="O9" t="n">
-        <v>0.4146</v>
+        <v>-0.5182</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.3887</v>
+        <v>-0.5952</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.9838</v>
+        <v>-2.9758</v>
       </c>
       <c r="R9" t="n">
-        <v>0.5952</v>
+        <v>2.3806</v>
       </c>
       <c r="S9" t="n">
-        <v>1.9981</v>
+        <v>-0.153</v>
       </c>
       <c r="T9" t="n">
-        <v>2.0123</v>
+        <v>0.1248</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0142</v>
+        <v>-0.2778</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.2065</v>
+        <v>1.2065</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.2065</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2065</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P. SAIZ FUENTES</t>
+          <t>J. ARNAL DIAZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1185,67 +1185,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.6342</v>
+        <v>-0.6042</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.537</v>
+        <v>-0.7499</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.09719999999999999</v>
+        <v>0.1456</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.0291</v>
+        <v>0.6065</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6395</v>
+        <v>0.872</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.6686</v>
+        <v>-0.2656</v>
       </c>
       <c r="J10" t="n">
-        <v>1.9464</v>
+        <v>-0.0244</v>
       </c>
       <c r="K10" t="n">
-        <v>2.0968</v>
+        <v>0.6558</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.1504</v>
+        <v>-0.6802</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.9755</v>
+        <v>0.6309</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.4573</v>
+        <v>0.2163</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.5182</v>
+        <v>0.4146</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.5952</v>
+        <v>-1.3887</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.9758</v>
+        <v>-1.9838</v>
       </c>
       <c r="R10" t="n">
-        <v>2.3806</v>
+        <v>0.5952</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.2164</v>
+        <v>1.3845</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7141</v>
+        <v>1.2584</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5023</v>
+        <v>0.1261</v>
       </c>
       <c r="V10" t="n">
-        <v>1.2065</v>
+        <v>-1.2065</v>
       </c>
       <c r="W10" t="n">
-        <v>1.2065</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="11">
@@ -1263,13 +1263,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.6296</v>
+        <v>-1.1325</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.6649</v>
+        <v>-0.3362</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.9646</v>
+        <v>-0.7963</v>
       </c>
       <c r="G11" t="n">
         <v>-1.9058</v>
@@ -1308,13 +1308,13 @@
         <v>0.7935</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7833</v>
+        <v>-0.2862</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3514</v>
+        <v>-0.0226</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4319</v>
+        <v>-0.2636</v>
       </c>
       <c r="V11" t="n">
         <v>0.266</v>
@@ -1341,13 +1341,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.2371</v>
+        <v>-1.1979</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.3501</v>
+        <v>-2.6756</v>
       </c>
       <c r="F12" t="n">
-        <v>1.113</v>
+        <v>1.4777</v>
       </c>
       <c r="G12" t="n">
         <v>-1.7302</v>
@@ -1386,13 +1386,13 @@
         <v>1.5871</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2329</v>
+        <v>0.8063</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0794</v>
+        <v>0.754</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3124</v>
+        <v>0.0524</v>
       </c>
       <c r="V12" t="n">
         <v>-0.8692</v>
@@ -1419,13 +1419,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.5226</v>
+        <v>-3.0139</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.0246</v>
+        <v>-3.2254</v>
       </c>
       <c r="F13" t="n">
-        <v>1.502</v>
+        <v>0.2115</v>
       </c>
       <c r="G13" t="n">
         <v>-2.2345</v>
@@ -1464,13 +1464,13 @@
         <v>2.579</v>
       </c>
       <c r="S13" t="n">
-        <v>2.1322</v>
+        <v>1.6409</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1758</v>
+        <v>0.975</v>
       </c>
       <c r="U13" t="n">
-        <v>1.9564</v>
+        <v>0.6657999999999999</v>
       </c>
       <c r="V13" t="n">
         <v>-2.0235</v>
@@ -1497,13 +1497,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-3.6114</v>
+        <v>-3.1946</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.8148</v>
+        <v>-0.6504</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.7967</v>
+        <v>-2.5442</v>
       </c>
       <c r="G14" t="n">
         <v>0.8745000000000001</v>
@@ -1542,13 +1542,13 @@
         <v>1.5871</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.073</v>
+        <v>-0.6561</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.5498</v>
+        <v>-0.3854</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.5232</v>
+        <v>-0.2707</v>
       </c>
       <c r="V14" t="n">
         <v>-3.0162</v>
@@ -1575,13 +1575,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.254500000000002</v>
+        <v>6.618600000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.783</v>
+        <v>1.1134</v>
       </c>
       <c r="F15" t="n">
-        <v>5.037199999999999</v>
+        <v>5.504899999999999</v>
       </c>
       <c r="G15" t="n">
         <v>-2.608099999999999</v>
@@ -1593,7 +1593,7 @@
         <v>-8.926500000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>2.5481</v>
+        <v>2.548100000000001</v>
       </c>
       <c r="K15" t="n">
         <v>10.8404</v>
@@ -1608,10 +1608,10 @@
         <v>-4.522</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.6341999999999999</v>
+        <v>-0.6342000000000001</v>
       </c>
       <c r="P15" t="n">
-        <v>1.586999999999999</v>
+        <v>1.587</v>
       </c>
       <c r="Q15" t="n">
         <v>-14.8787</v>
@@ -1620,16 +1620,16 @@
         <v>16.4659</v>
       </c>
       <c r="S15" t="n">
-        <v>4.826600000000001</v>
+        <v>8.190799999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>4.676999999999999</v>
+        <v>7.5736</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1494999999999999</v>
+        <v>0.6171</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.5510999999999999</v>
+        <v>-0.5511000000000008</v>
       </c>
       <c r="W15" t="n">
         <v>5.8706</v>
@@ -1641,7 +1641,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>B. ZICOVICH</t>
+          <t>J. MALO MONTORIO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1653,73 +1653,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.0319</v>
+        <v>4.6392</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9897</v>
+        <v>2.7569</v>
       </c>
       <c r="F16" t="n">
-        <v>3.0421</v>
+        <v>1.8824</v>
       </c>
       <c r="G16" t="n">
-        <v>2.3882</v>
+        <v>-0.1919</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2466</v>
+        <v>0.1269</v>
       </c>
       <c r="I16" t="n">
-        <v>2.1416</v>
+        <v>-0.3187</v>
       </c>
       <c r="J16" t="n">
-        <v>0.7459</v>
+        <v>0.6298</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1008</v>
+        <v>1.3826</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6451</v>
+        <v>-0.7529</v>
       </c>
       <c r="M16" t="n">
-        <v>1.6422</v>
+        <v>-0.8216</v>
       </c>
       <c r="N16" t="n">
-        <v>0.1458</v>
+        <v>-1.2557</v>
       </c>
       <c r="O16" t="n">
-        <v>1.4964</v>
+        <v>0.4341</v>
       </c>
       <c r="P16" t="n">
-        <v>0.7935</v>
+        <v>-0.7935</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-3.1741</v>
       </c>
       <c r="R16" t="n">
-        <v>0.7935</v>
+        <v>2.3806</v>
       </c>
       <c r="S16" t="n">
-        <v>0.8501</v>
+        <v>0.1955</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2438</v>
+        <v>-0.0566</v>
       </c>
       <c r="U16" t="n">
-        <v>0.6064000000000001</v>
+        <v>0.2521</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>5.4291</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>5.3578</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>0.0713</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. MALO MONTORIO</t>
+          <t>B. ZICOVICH</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1731,67 +1731,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.7771</v>
+        <v>3.5388</v>
       </c>
       <c r="E17" t="n">
-        <v>2.2467</v>
+        <v>0.7857</v>
       </c>
       <c r="F17" t="n">
-        <v>1.5304</v>
+        <v>2.7531</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.1919</v>
+        <v>2.3882</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1269</v>
+        <v>0.2466</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.3187</v>
+        <v>2.1416</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6298</v>
+        <v>0.7459</v>
       </c>
       <c r="K17" t="n">
-        <v>1.3826</v>
+        <v>0.1008</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.7529</v>
+        <v>0.6451</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.8216</v>
+        <v>1.6422</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.2557</v>
+        <v>0.1458</v>
       </c>
       <c r="O17" t="n">
-        <v>0.4341</v>
+        <v>1.4964</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.7935</v>
+        <v>0.7935</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.1741</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.3806</v>
+        <v>0.7935</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6666</v>
+        <v>0.357</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5667</v>
+        <v>0.0397</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0999</v>
+        <v>0.3173</v>
       </c>
       <c r="V17" t="n">
-        <v>5.4291</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>5.3578</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0.0713</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1809,13 +1809,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.2613</v>
+        <v>1.6515</v>
       </c>
       <c r="E18" t="n">
-        <v>1.9047</v>
+        <v>1.8026</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.6434</v>
+        <v>-0.1511</v>
       </c>
       <c r="G18" t="n">
         <v>0.9906</v>
@@ -1854,13 +1854,13 @@
         <v>0.7935</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.7374000000000001</v>
+        <v>-0.3472</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0567</v>
+        <v>-0.0453</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.7942</v>
+        <v>-0.3019</v>
       </c>
       <c r="V18" t="n">
         <v>1.2065</v>
@@ -1887,13 +1887,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0163</v>
+        <v>0.4346</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.2685</v>
+        <v>-1.3705</v>
       </c>
       <c r="F19" t="n">
-        <v>1.2847</v>
+        <v>1.8051</v>
       </c>
       <c r="G19" t="n">
         <v>-2.2643</v>
@@ -1932,13 +1932,13 @@
         <v>2.3806</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.7187</v>
+        <v>-0.3004</v>
       </c>
       <c r="T19" t="n">
-        <v>0.3005</v>
+        <v>0.1985</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.0192</v>
+        <v>-0.4989</v>
       </c>
       <c r="V19" t="n">
         <v>0.8171</v>
@@ -1953,7 +1953,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>U. LATORRE CIRIA</t>
+          <t>R. GER SIERRA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1965,73 +1965,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0119</v>
+        <v>-0.0106</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3845</v>
+        <v>-1.9828</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3725</v>
+        <v>1.9722</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1408</v>
+        <v>0.202</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.7156</v>
+        <v>-2.2829</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8564000000000001</v>
+        <v>2.4849</v>
       </c>
       <c r="J20" t="n">
-        <v>0.3277</v>
+        <v>0.2957</v>
       </c>
       <c r="K20" t="n">
-        <v>0.2876</v>
+        <v>-0.9519</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0402</v>
+        <v>1.2476</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.187</v>
+        <v>-0.09370000000000001</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.0032</v>
+        <v>-1.3311</v>
       </c>
       <c r="O20" t="n">
-        <v>0.8162</v>
+        <v>1.2374</v>
       </c>
       <c r="P20" t="n">
-        <v>0.7935</v>
+        <v>-0.5952</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-2.1822</v>
       </c>
       <c r="R20" t="n">
-        <v>0.7935</v>
+        <v>1.5871</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6564</v>
+        <v>-0.2919</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0567</v>
+        <v>-0.0963</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.7131</v>
+        <v>-0.1957</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.266</v>
+        <v>0.6745</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.266</v>
+        <v>0.6745</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X. ROSÀS MARCO</t>
+          <t>U. LATORRE CIRIA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2043,73 +2043,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.9872</v>
+        <v>-0.1904</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1743</v>
+        <v>0.0784</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.1615</v>
+        <v>-0.2688</v>
       </c>
       <c r="G21" t="n">
-        <v>0.9129</v>
+        <v>0.1408</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.9877</v>
+        <v>-0.7156</v>
       </c>
       <c r="I21" t="n">
-        <v>1.9006</v>
+        <v>0.8564000000000001</v>
       </c>
       <c r="J21" t="n">
-        <v>1.8982</v>
+        <v>0.3277</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0106</v>
+        <v>0.2876</v>
       </c>
       <c r="L21" t="n">
-        <v>1.8876</v>
+        <v>0.0402</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.9853</v>
+        <v>-0.187</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.9983</v>
+        <v>-1.0032</v>
       </c>
       <c r="O21" t="n">
-        <v>0.013</v>
+        <v>0.8162</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.9919</v>
+        <v>0.7935</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.1822</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1903</v>
+        <v>0.7935</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.9795</v>
+        <v>-0.8587</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7481</v>
+        <v>-0.2493</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2313</v>
+        <v>-0.6094000000000001</v>
       </c>
       <c r="V21" t="n">
-        <v>0.0713</v>
+        <v>-0.266</v>
       </c>
       <c r="W21" t="n">
-        <v>1.2065</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.1352</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>R. GER SIERRA</t>
+          <t>X. ROSÀS MARCO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2121,67 +2121,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.0768</v>
+        <v>-0.1948</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.697</v>
+        <v>0.5824</v>
       </c>
       <c r="F22" t="n">
-        <v>1.6202</v>
+        <v>-0.7772</v>
       </c>
       <c r="G22" t="n">
-        <v>0.202</v>
+        <v>0.9129</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.2829</v>
+        <v>-0.9877</v>
       </c>
       <c r="I22" t="n">
-        <v>2.4849</v>
+        <v>1.9006</v>
       </c>
       <c r="J22" t="n">
-        <v>0.2957</v>
+        <v>1.8982</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.9519</v>
+        <v>0.0106</v>
       </c>
       <c r="L22" t="n">
-        <v>1.2476</v>
+        <v>1.8876</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.09370000000000001</v>
+        <v>-0.9853</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.3311</v>
+        <v>-0.9983</v>
       </c>
       <c r="O22" t="n">
-        <v>1.2374</v>
+        <v>0.013</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.5952</v>
+        <v>-0.9919</v>
       </c>
       <c r="Q22" t="n">
         <v>-2.1822</v>
       </c>
       <c r="R22" t="n">
-        <v>1.5871</v>
+        <v>1.1903</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.3581</v>
+        <v>-0.187</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8105</v>
+        <v>-0.34</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5477</v>
+        <v>0.153</v>
       </c>
       <c r="V22" t="n">
-        <v>0.6745</v>
+        <v>0.0713</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.2065</v>
       </c>
       <c r="X22" t="n">
-        <v>0.6745</v>
+        <v>-1.1352</v>
       </c>
     </row>
     <row r="23">
@@ -2199,13 +2199,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.6422</v>
+        <v>-1.9559</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.366</v>
+        <v>-2.2843</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.2762</v>
+        <v>0.3283</v>
       </c>
       <c r="G23" t="n">
         <v>1.8536</v>
@@ -2244,13 +2244,13 @@
         <v>2.579</v>
       </c>
       <c r="S23" t="n">
-        <v>0.6468</v>
+        <v>0.333</v>
       </c>
       <c r="T23" t="n">
-        <v>1.4739</v>
+        <v>0.5556</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.8270999999999999</v>
+        <v>-0.2226</v>
       </c>
       <c r="V23" t="n">
         <v>-2.5555</v>
@@ -2277,13 +2277,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.2226</v>
+        <v>-3.0602</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.0783</v>
+        <v>-1.3844</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.1443</v>
+        <v>-1.6758</v>
       </c>
       <c r="G24" t="n">
         <v>-0.9009</v>
@@ -2322,13 +2322,13 @@
         <v>0.5952</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.5039</v>
+        <v>-0.3415</v>
       </c>
       <c r="T24" t="n">
-        <v>0.1814</v>
+        <v>-0.1247</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.6853</v>
+        <v>-0.2168</v>
       </c>
       <c r="V24" t="n">
         <v>-2.4129</v>
@@ -2355,13 +2355,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.6591</v>
+        <v>-3.9407</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.3107</v>
+        <v>-3.0046</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.3485</v>
+        <v>-0.9361</v>
       </c>
       <c r="G25" t="n">
         <v>-0.4182</v>
@@ -2400,13 +2400,13 @@
         <v>1.7855</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.6296</v>
+        <v>-0.9112</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.8105</v>
+        <v>-0.5044</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.8191000000000001</v>
+        <v>-0.4068</v>
       </c>
       <c r="V25" t="n">
         <v>-2.4129</v>
@@ -2433,19 +2433,19 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-2.489399999999999</v>
+        <v>0.9115000000000006</v>
       </c>
       <c r="E26" t="n">
         <v>-4.020600000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>1.531</v>
+        <v>4.932100000000001</v>
       </c>
       <c r="G26" t="n">
         <v>2.7128</v>
       </c>
       <c r="H26" t="n">
-        <v>-6.097300000000001</v>
+        <v>-6.0973</v>
       </c>
       <c r="I26" t="n">
         <v>8.8101</v>
@@ -2478,13 +2478,13 @@
         <v>14.8788</v>
       </c>
       <c r="S26" t="n">
-        <v>-5.7533</v>
+        <v>-2.3524</v>
       </c>
       <c r="T26" t="n">
         <v>-0.6228</v>
       </c>
       <c r="U26" t="n">
-        <v>-5.1305</v>
+        <v>-1.7297</v>
       </c>
       <c r="V26" t="n">
         <v>0.5512000000000006</v>
